--- a/tests/fixtures/03_purchase_order/03_purchase_order_pattern-from-claude.xlsx
+++ b/tests/fixtures/03_purchase_order/03_purchase_order_pattern-from-claude.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -950,34 +950,39 @@
       <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>col_grand_total</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>po_label</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -987,7 +992,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>po.number</t>
+          <t>po_label</t>
         </is>
       </c>
       <c r="C23" s="5" t="n"/>
@@ -1004,7 +1009,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>date_label</t>
+          <t>po.number</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -1021,7 +1026,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>po.date</t>
+          <t>date_label</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -1038,7 +1043,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>vendor_label</t>
+          <t>po.date</t>
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -1055,7 +1060,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>po.vendor</t>
+          <t>vendor_label</t>
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
@@ -1072,7 +1077,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>ref_label</t>
+          <t>po.vendor</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -1089,7 +1094,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>po.ref</t>
+          <t>ref_label</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -1099,96 +1104,145 @@
       <c r="G29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>po.ref</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>col_item</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>col_description</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>col_qty</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>col_unit_price</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>col_total</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>line.item</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>line.description</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>line.qty</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>line.unit_price</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>line.total</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FOOTER:1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>col_grand_total</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
